--- a/CSV/Timelines.xlsx
+++ b/CSV/Timelines.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\1Data\1study\WebLearn\Timeline\CSV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE7A8802-1BEE-4361-8EB2-AF50451E2FC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B687258-AB27-4476-9697-ADDB105929AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21840" activeTab="1" xr2:uid="{A53E62BE-B75E-4C3C-A768-5CF0DB6D2C01}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" activeTab="3" xr2:uid="{A53E62BE-B75E-4C3C-A768-5CF0DB6D2C01}"/>
   </bookViews>
   <sheets>
     <sheet name="ThreeBody" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1023" uniqueCount="767">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1039" uniqueCount="783">
   <si>
     <t>Year</t>
   </si>
@@ -31,7 +31,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Lable</t>
+    <t>Label</t>
   </si>
   <si>
     <t>Importance</t>
@@ -2551,6 +2551,72 @@
   </si>
   <si>
     <t>中共十八大召开，提出实现中华民族伟大复兴的中国梦，中国特色社会主义进入新时代。</t>
+  </si>
+  <si>
+    <t>薛定谔提出波动方程</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>1925年，埃尔文·薛定谔信任了德布罗意的思想。为了描述电子能量不连续的现象，他将电子看成德布罗意波，用一个波动方程去表示他。最后求出了薛定谔波动方程，于1926年正式发表论文，彻底建立了波动力学。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>薛定谔波动力学</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>波动与矩阵等价</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>1926年4月，薛定谔、泡利、约尔当都各自证明了两种力学在数学上来说是完全等价的。它们都是从经典的哈密顿函数而来，只不过一个是从粒子的方程出发，另一个是从波动方程出发罢了。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>波动力学与矩阵力学在数学上等价</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>1926年7月，波恩将薛定谔波函数解释为骰子。它代表的是一种随机、一种概率，而绝不是薛定谔本人所理解的电子电荷在空间中的实际分布。波恩表示，波动函数的平方，代表了电子在某个地点出现的“概率”。电子本身不会像波那样扩展开去，但是它的出现概率则像一个波，严格地按照波函数的分布所展开。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>海森堡发表不确定性原理</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>海森堡测不准原理</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>1927年，海森堡发现，在矩阵力学中p×q≠q×p，这就是说，先观测动量p，再观测位置q，这和先观测q再观测p，其结果是不一样的。他认为，为了测量电子的位置，我们剧烈地改变了它的速度，也就是动量。我们没法同时既准确知道一个电子的位置，同时又准确地了解它的动量。
+海森堡最后得出了一个公式：Δp×Δq &gt; h/4π，他于1927年3月23日将其在《物理学杂志》上发表。
+我们无法同时准确知道p和q的信息，这种奇特的量被称为“共轭量”，这样的量还有许多。比如能量E和时间t，二者关系为：ΔE×Δt &gt; h。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>引力波被证实</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>LIGO项目证实引力波存在</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>玻尔互补原理</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>玻尔提出互补原理</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>玻恩定则：骰子</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>波恩将薛定谔波函数解释为骰子（概率解释）</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -8396,7 +8462,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32EFCE5F-2013-44CD-9DFE-6E90EE4F7B11}">
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.75" style="2" customWidth="1"/>
@@ -8895,7 +8961,7 @@
         <v>124</v>
       </c>
       <c r="F25" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>125</v>
@@ -8961,18 +9027,132 @@
         <v>130</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:8" ht="57" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
+        <v>1926</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>769</v>
+      </c>
+      <c r="F29" s="1">
+        <v>3</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>767</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A30" s="2">
+        <v>1926</v>
+      </c>
+      <c r="B30" s="1">
+        <v>4</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>770</v>
+      </c>
+      <c r="F30" s="1">
+        <v>0</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>772</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="71.25" x14ac:dyDescent="0.2">
+      <c r="A31" s="2">
+        <v>1926</v>
+      </c>
+      <c r="B31" s="1">
+        <v>7</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>781</v>
+      </c>
+      <c r="F31" s="1">
+        <v>3</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>782</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="142.5" x14ac:dyDescent="0.2">
+      <c r="A32" s="2">
         <v>1927</v>
       </c>
-      <c r="D29" s="1" t="s">
+      <c r="B32" s="1">
+        <v>3</v>
+      </c>
+      <c r="C32" s="3">
+        <v>23</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>775</v>
+      </c>
+      <c r="F32" s="1">
+        <v>3</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>774</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A33" s="2">
+        <v>1927</v>
+      </c>
+      <c r="B33" s="1">
+        <v>9</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>779</v>
+      </c>
+      <c r="F33" s="1">
+        <v>3</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A34" s="2">
+        <v>1927</v>
+      </c>
+      <c r="B34" s="1">
+        <v>-11</v>
+      </c>
+      <c r="D34" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="F29" s="1">
-        <v>0</v>
-      </c>
-      <c r="H29" s="1" t="s">
+      <c r="F34" s="1">
+        <v>0</v>
+      </c>
+      <c r="H34" s="1" t="s">
         <v>121</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A35" s="2">
+        <v>2016</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>777</v>
+      </c>
+      <c r="F35" s="1">
+        <v>5</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>778</v>
       </c>
     </row>
   </sheetData>
